--- a/sources/table_normalization/xlsx/economy-table113.xlsx
+++ b/sources/table_normalization/xlsx/economy-table113.xlsx
@@ -197,7 +197,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -216,6 +216,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -231,7 +237,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -241,13 +247,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -731,7 +743,7 @@
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:13" ht="70">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
@@ -749,69 +761,69 @@
     </row>
     <row r="2" spans="1:13" ht="42">
       <c r="A2" s="2"/>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="M2" s="4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="17.5" customHeight="1">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
     </row>
     <row r="4" spans="1:13" ht="17.5" customHeight="1">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
@@ -892,11 +904,11 @@
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
@@ -994,11 +1006,11 @@
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
@@ -1181,11 +1193,11 @@
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
-      <c r="D26" s="3" t="s">
+      <c r="D26" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
